--- a/JsonConverter/ExcelFiles/Quest.xlsx
+++ b/JsonConverter/ExcelFiles/Quest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SunnyHoGaming\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5377AF34-4991-4DFC-83AD-5A20A6299A4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0390F84D-35BC-45AE-AE47-19B21BA62ED8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="46">
   <si>
     <t>Id</t>
   </si>
@@ -39,10 +39,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Quest_Day1_001</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>퀘스트 내용</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -71,43 +67,136 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>1일차 퀘스트: 고장난 모든 기능을 수리하시오</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>2일차 퀘스트: 폭주한 픽서들을 진정시키시오</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>3일차 퀘스트: 픽서를 통해 식량을 획득하십시오.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>표시되어 있는 곳에서 기능을 직접 수리하자</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>표시되어 있는 방으로 가서 픽서들을 진정시키자</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>4일차 퀘스트: 지구에 구조 요청하시오</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>픽서에게 식량 수급을 지시하자</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>5일차 퀘스트: 최선을 다해 생존하시오</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>픽서와 함께 구조대를 기다리자</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>픽서가 가지고온 위성전화로 지구와 통신하자</t>
+    <t>퀘스트 타입</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Type</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Main</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DayQuest</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Quest_Day_001</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>해금 날짜</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>UnlockDay</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>퀘스트 세부 사항</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SubTasks</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>퀘스트 이름</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">string </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>QuestName</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인 퀘스트</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2일차 퀘스트</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3일차 퀘스트</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>4일차 퀘스트</t>
+  </si>
+  <si>
+    <t>5일차 퀘스트</t>
+  </si>
+  <si>
+    <t>고장난 모든 기능을 수리하시오</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>폭주한 픽서들을 진정시키시오</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>지구에 구조 요청하시오</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>최선을 다해 생존하시오</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>픽서를 통해 식량을 획득하십시오</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>산소 공급 장치 수리:OxygenSupply|전력 공급 장치 수리:PowerSupply|온도 제어 장치 수리:TemperatureControl|항로 제어 장치 수리:RouteControl</t>
+  </si>
+  <si>
+    <t>산소 공급 장치 수리:OxygenSupply|전력 공급 장치 수리:PowerSupply|온도 제어 장치 수리:TemperatureControl|항로 제어 장치 수리:RouteControl</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>획득한 아이템을 참고하여 픽서를 진정시키자!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>픽서 부르미 획득하기:Item:Item_Map_01|폭주한 픽서 진정시키기 (1):Task:FixerCalm_1|폭주한 픽서 진정시키기 (2):Task:FixerCalm_2|폭주한 픽서 진정시키기 (3):Task:FixerCalm_3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>픽서에게 식당에서 음식 픽업 업무 시키기:FoodSupply</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>위성전화를 작동시켜 올바른 번호를 입력하자:Task:SatellitePhone</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>픽서와 함께 힘을 합쳐 기능을 수리 하자!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>픽서에게 식량 수급을 지시하자!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>표시되어 있는 곳에서 기능을 직접 수리하자!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>픽서가 가지고온 위성전화로 지구와 통신하자!</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -237,7 +326,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -290,6 +379,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -508,250 +599,493 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C1000"/>
+  <dimension ref="A1:H1000"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="31.85546875" customWidth="1"/>
-    <col min="2" max="2" width="50.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="49" bestFit="1" customWidth="1"/>
+    <col min="1" max="4" width="31.85546875" customWidth="1"/>
+    <col min="5" max="5" width="50.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="49" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="198.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="49" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" customHeight="1">
+    <row r="1" spans="1:8" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15.75" customHeight="1">
+        <v>12</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" s="14"/>
+    </row>
+    <row r="2" spans="1:8" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" customHeight="1">
+      <c r="F2" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="14"/>
+    </row>
+    <row r="3" spans="1:8" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="15" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="15.75" customHeight="1">
+      <c r="G3" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="15"/>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="15.75" customHeight="1">
+        <v>14</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="10">
+        <v>1</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4" s="16"/>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="10">
+        <v>2</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" s="16"/>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A6" s="3" t="s">
         <v>7</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A6" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="16" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="15.75" customHeight="1">
+      <c r="C6" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="10">
+        <v>3</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" s="16"/>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" customHeight="1">
       <c r="A7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="10">
+        <v>4</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7" s="16"/>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A8" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="B8" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="15.75" customHeight="1">
+        <v>15</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="10">
+        <v>5</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" s="17"/>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" customHeight="1">
       <c r="A9" s="3"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="17"/>
-    </row>
-    <row r="10" spans="1:3" ht="15.75" customHeight="1">
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" customHeight="1">
       <c r="A10" s="3"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="18"/>
-    </row>
-    <row r="11" spans="1:3" ht="15.75" customHeight="1">
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" customHeight="1">
       <c r="A11" s="3"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="18"/>
-    </row>
-    <row r="12" spans="1:3" ht="15.75" customHeight="1">
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" customHeight="1">
       <c r="A12" s="3"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="17"/>
-    </row>
-    <row r="13" spans="1:3" ht="15.75" customHeight="1">
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" customHeight="1">
       <c r="A13" s="3"/>
       <c r="B13" s="10"/>
-      <c r="C13" s="16"/>
-    </row>
-    <row r="14" spans="1:3" ht="15.75" customHeight="1">
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" customHeight="1">
       <c r="A14" s="4"/>
       <c r="B14" s="12"/>
-      <c r="C14" s="18"/>
-    </row>
-    <row r="15" spans="1:3" ht="15.75" customHeight="1">
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" customHeight="1">
       <c r="A15" s="4"/>
       <c r="B15" s="12"/>
-      <c r="C15" s="18"/>
-    </row>
-    <row r="16" spans="1:3" ht="15.75" customHeight="1">
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" customHeight="1">
       <c r="A16" s="5"/>
       <c r="B16" s="13"/>
-      <c r="C16" s="19"/>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" customHeight="1">
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+    </row>
+    <row r="17" spans="1:8" ht="15.75" customHeight="1">
       <c r="A17" s="5"/>
       <c r="B17" s="13"/>
-      <c r="C17" s="19"/>
-    </row>
-    <row r="18" spans="1:3" ht="15.75" customHeight="1">
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+    </row>
+    <row r="18" spans="1:8" ht="15.75" customHeight="1">
       <c r="A18" s="5"/>
       <c r="B18" s="13"/>
-      <c r="C18" s="19"/>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" customHeight="1">
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+    </row>
+    <row r="19" spans="1:8" ht="15.75" customHeight="1">
       <c r="A19" s="5"/>
       <c r="B19" s="13"/>
-      <c r="C19" s="19"/>
-    </row>
-    <row r="20" spans="1:3" ht="15.75" customHeight="1">
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+    </row>
+    <row r="20" spans="1:8" ht="15.75" customHeight="1">
       <c r="A20" s="5"/>
       <c r="B20" s="13"/>
-      <c r="C20" s="19"/>
-    </row>
-    <row r="21" spans="1:3" ht="15.75" customHeight="1">
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" customHeight="1">
       <c r="A21" s="5"/>
       <c r="B21" s="13"/>
-      <c r="C21" s="19"/>
-    </row>
-    <row r="22" spans="1:3" ht="15.75" customHeight="1">
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+    </row>
+    <row r="22" spans="1:8" ht="15.75" customHeight="1">
       <c r="A22" s="5"/>
       <c r="B22" s="13"/>
-      <c r="C22" s="19"/>
-    </row>
-    <row r="23" spans="1:3" ht="15.75" customHeight="1">
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+    </row>
+    <row r="23" spans="1:8" ht="15.75" customHeight="1">
       <c r="A23" s="5"/>
       <c r="B23" s="13"/>
-      <c r="C23" s="19"/>
-    </row>
-    <row r="24" spans="1:3" ht="15.75" customHeight="1">
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+    </row>
+    <row r="24" spans="1:8" ht="15.75" customHeight="1">
       <c r="A24" s="5"/>
       <c r="B24" s="13"/>
-      <c r="C24" s="19"/>
-    </row>
-    <row r="25" spans="1:3" ht="15.75" customHeight="1">
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+    </row>
+    <row r="25" spans="1:8" ht="15.75" customHeight="1">
       <c r="A25" s="5"/>
       <c r="B25" s="13"/>
-      <c r="C25" s="19"/>
-    </row>
-    <row r="26" spans="1:3" ht="15.75" customHeight="1">
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+    </row>
+    <row r="26" spans="1:8" ht="15.75" customHeight="1">
       <c r="A26" s="6"/>
       <c r="B26" s="20"/>
-      <c r="C26" s="22"/>
-    </row>
-    <row r="27" spans="1:3" ht="15.75" customHeight="1">
+      <c r="C26" s="20"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="24"/>
+      <c r="H26" s="24"/>
+    </row>
+    <row r="27" spans="1:8" ht="15.75" customHeight="1">
       <c r="A27" s="6"/>
       <c r="B27" s="20"/>
-      <c r="C27" s="22"/>
-    </row>
-    <row r="28" spans="1:3" ht="15.75" customHeight="1">
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="24"/>
+      <c r="H27" s="24"/>
+    </row>
+    <row r="28" spans="1:8" ht="15.75" customHeight="1">
       <c r="A28" s="6"/>
       <c r="B28" s="20"/>
-      <c r="C28" s="22"/>
-    </row>
-    <row r="29" spans="1:3" ht="15.75" customHeight="1">
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="24"/>
+      <c r="H28" s="24"/>
+    </row>
+    <row r="29" spans="1:8" ht="15.75" customHeight="1">
       <c r="A29" s="6"/>
       <c r="B29" s="20"/>
-      <c r="C29" s="22"/>
-    </row>
-    <row r="30" spans="1:3" ht="15.75" customHeight="1">
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="24"/>
+      <c r="H29" s="24"/>
+    </row>
+    <row r="30" spans="1:8" ht="15.75" customHeight="1">
       <c r="A30" s="6"/>
       <c r="B30" s="20"/>
-      <c r="C30" s="22"/>
-    </row>
-    <row r="31" spans="1:3" ht="15.75" customHeight="1">
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="24"/>
+      <c r="H30" s="24"/>
+    </row>
+    <row r="31" spans="1:8" ht="15.75" customHeight="1">
       <c r="A31" s="6"/>
       <c r="B31" s="20"/>
-      <c r="C31" s="22"/>
-    </row>
-    <row r="32" spans="1:3" ht="15.75" customHeight="1">
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="24"/>
+      <c r="H31" s="24"/>
+    </row>
+    <row r="32" spans="1:8" ht="15.75" customHeight="1">
       <c r="A32" s="7"/>
       <c r="B32" s="21"/>
-      <c r="C32" s="23"/>
-    </row>
-    <row r="33" spans="1:3" ht="15.75" customHeight="1">
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="23"/>
+      <c r="G32" s="25"/>
+      <c r="H32" s="25"/>
+    </row>
+    <row r="33" spans="1:8" ht="15.75" customHeight="1">
       <c r="A33" s="7"/>
       <c r="B33" s="21"/>
-      <c r="C33" s="23"/>
-    </row>
-    <row r="34" spans="1:3" ht="15.75" customHeight="1">
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
+    </row>
+    <row r="34" spans="1:8" ht="15.75" customHeight="1">
       <c r="A34" s="7"/>
       <c r="B34" s="21"/>
-      <c r="C34" s="23"/>
-    </row>
-    <row r="35" spans="1:3" ht="15.75" customHeight="1">
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="23"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="25"/>
+    </row>
+    <row r="35" spans="1:8" ht="15.75" customHeight="1">
       <c r="A35" s="7"/>
       <c r="B35" s="21"/>
-      <c r="C35" s="23"/>
-    </row>
-    <row r="36" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="37" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="38" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="39" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="40" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="41" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="42" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="43" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="44" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="45" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="46" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="47" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="48" spans="1:3" ht="15.75" customHeight="1"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="23"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="25"/>
+    </row>
+    <row r="36" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="37" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="38" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="39" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="40" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="41" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="42" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="43" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="44" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="45" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="46" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="47" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="48" spans="1:8" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/Quest.xlsx
+++ b/JsonConverter/ExcelFiles/Quest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SunnyHoGaming\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0390F84D-35BC-45AE-AE47-19B21BA62ED8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{814894F0-75CF-4FB2-ABE9-4BC5EB1B4246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="45">
   <si>
     <t>Id</t>
   </si>
@@ -80,10 +80,6 @@
   </si>
   <si>
     <t>DayQuest</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -231,7 +227,7 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -253,19 +249,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFD86DCD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -326,7 +310,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -337,12 +321,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -352,13 +330,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -368,19 +339,9 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -599,493 +560,239 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H1000"/>
+  <dimension ref="A1:G890"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="31.85546875" customWidth="1"/>
     <col min="5" max="5" width="50.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="49" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="198.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="49" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" customHeight="1">
+    <row r="1" spans="1:7" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="C1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="H1" s="14"/>
+      <c r="G1" s="7" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" ht="15.75" customHeight="1">
+    <row r="2" spans="1:7" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="8" t="s">
+      <c r="C2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="14"/>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1">
+    <row r="3" spans="1:7" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="15"/>
+      <c r="D4" s="6">
+        <v>1</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="10">
-        <v>1</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="G4" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="H4" s="16"/>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1">
+    <row r="5" spans="1:7" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="10">
+      <c r="C5" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="6">
         <v>2</v>
       </c>
-      <c r="E5" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" s="16" t="s">
+      <c r="E5" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="H5" s="16"/>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1">
+    <row r="6" spans="1:7" ht="15.75" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="10">
+      <c r="C6" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="6">
         <v>3</v>
       </c>
-      <c r="E6" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="G6" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="H6" s="16"/>
+      <c r="E6" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1">
+    <row r="7" spans="1:7" ht="15.75" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="10">
+      <c r="C7" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="6">
         <v>4</v>
       </c>
-      <c r="E7" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="H7" s="16"/>
+      <c r="E7" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1">
+    <row r="8" spans="1:7" ht="15.75" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="10">
+      <c r="C8" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="6">
         <v>5</v>
       </c>
-      <c r="E8" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="H8" s="17"/>
+      <c r="E8" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A9" s="3"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
-    </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A10" s="3"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
-    </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A11" s="3"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
-    </row>
-    <row r="12" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A12" s="3"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-    </row>
-    <row r="13" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A13" s="3"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-    </row>
-    <row r="14" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A14" s="4"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
-    </row>
-    <row r="15" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A15" s="4"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-    </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A16" s="5"/>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-    </row>
-    <row r="17" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A17" s="5"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-    </row>
-    <row r="18" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A18" s="5"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-    </row>
-    <row r="19" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A19" s="5"/>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
-    </row>
-    <row r="20" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A20" s="5"/>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
-    </row>
-    <row r="21" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A21" s="5"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-    </row>
-    <row r="22" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A22" s="5"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
-    </row>
-    <row r="23" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A23" s="5"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
-    </row>
-    <row r="24" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A24" s="5"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-    </row>
-    <row r="25" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A25" s="5"/>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-    </row>
-    <row r="26" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A26" s="6"/>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="24"/>
-      <c r="H26" s="24"/>
-    </row>
-    <row r="27" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A27" s="6"/>
-      <c r="B27" s="20"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="24"/>
-      <c r="H27" s="24"/>
-    </row>
-    <row r="28" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A28" s="6"/>
-      <c r="B28" s="20"/>
-      <c r="C28" s="20"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="24"/>
-      <c r="H28" s="24"/>
-    </row>
-    <row r="29" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A29" s="6"/>
-      <c r="B29" s="20"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="24"/>
-      <c r="H29" s="24"/>
-    </row>
-    <row r="30" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A30" s="6"/>
-      <c r="B30" s="20"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="22"/>
-      <c r="G30" s="24"/>
-      <c r="H30" s="24"/>
-    </row>
-    <row r="31" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A31" s="6"/>
-      <c r="B31" s="20"/>
-      <c r="C31" s="20"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="24"/>
-      <c r="H31" s="24"/>
-    </row>
-    <row r="32" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A32" s="7"/>
-      <c r="B32" s="21"/>
-      <c r="C32" s="21"/>
-      <c r="D32" s="21"/>
-      <c r="E32" s="21"/>
-      <c r="F32" s="23"/>
-      <c r="G32" s="25"/>
-      <c r="H32" s="25"/>
-    </row>
-    <row r="33" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A33" s="7"/>
-      <c r="B33" s="21"/>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="25"/>
-      <c r="H33" s="25"/>
-    </row>
-    <row r="34" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A34" s="7"/>
-      <c r="B34" s="21"/>
-      <c r="C34" s="21"/>
-      <c r="D34" s="21"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="23"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="25"/>
-    </row>
-    <row r="35" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A35" s="7"/>
-      <c r="B35" s="21"/>
-      <c r="C35" s="21"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="23"/>
-      <c r="G35" s="25"/>
-      <c r="H35" s="25"/>
-    </row>
-    <row r="36" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="37" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="38" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="39" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="40" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="41" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="42" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="43" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="44" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="45" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="46" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="47" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="48" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="9" spans="1:7" ht="15.75" customHeight="1"/>
+    <row r="10" spans="1:7" ht="15.75" customHeight="1"/>
+    <row r="11" spans="1:7" ht="15.75" customHeight="1"/>
+    <row r="12" spans="1:7" ht="15.75" customHeight="1"/>
+    <row r="13" spans="1:7" ht="15.75" customHeight="1"/>
+    <row r="14" spans="1:7" ht="15.75" customHeight="1"/>
+    <row r="15" spans="1:7" ht="15.75" customHeight="1"/>
+    <row r="16" spans="1:7" ht="15.75" customHeight="1"/>
+    <row r="17" ht="15.75" customHeight="1"/>
+    <row r="18" ht="15.75" customHeight="1"/>
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1"/>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>
@@ -1928,116 +1635,6 @@
     <row r="888" ht="15.75" customHeight="1"/>
     <row r="889" ht="15.75" customHeight="1"/>
     <row r="890" ht="15.75" customHeight="1"/>
-    <row r="891" ht="15.75" customHeight="1"/>
-    <row r="892" ht="15.75" customHeight="1"/>
-    <row r="893" ht="15.75" customHeight="1"/>
-    <row r="894" ht="15.75" customHeight="1"/>
-    <row r="895" ht="15.75" customHeight="1"/>
-    <row r="896" ht="15.75" customHeight="1"/>
-    <row r="897" ht="15.75" customHeight="1"/>
-    <row r="898" ht="15.75" customHeight="1"/>
-    <row r="899" ht="15.75" customHeight="1"/>
-    <row r="900" ht="15.75" customHeight="1"/>
-    <row r="901" ht="15.75" customHeight="1"/>
-    <row r="902" ht="15.75" customHeight="1"/>
-    <row r="903" ht="15.75" customHeight="1"/>
-    <row r="904" ht="15.75" customHeight="1"/>
-    <row r="905" ht="15.75" customHeight="1"/>
-    <row r="906" ht="15.75" customHeight="1"/>
-    <row r="907" ht="15.75" customHeight="1"/>
-    <row r="908" ht="15.75" customHeight="1"/>
-    <row r="909" ht="15.75" customHeight="1"/>
-    <row r="910" ht="15.75" customHeight="1"/>
-    <row r="911" ht="15.75" customHeight="1"/>
-    <row r="912" ht="15.75" customHeight="1"/>
-    <row r="913" ht="15.75" customHeight="1"/>
-    <row r="914" ht="15.75" customHeight="1"/>
-    <row r="915" ht="15.75" customHeight="1"/>
-    <row r="916" ht="15.75" customHeight="1"/>
-    <row r="917" ht="15.75" customHeight="1"/>
-    <row r="918" ht="15.75" customHeight="1"/>
-    <row r="919" ht="15.75" customHeight="1"/>
-    <row r="920" ht="15.75" customHeight="1"/>
-    <row r="921" ht="15.75" customHeight="1"/>
-    <row r="922" ht="15.75" customHeight="1"/>
-    <row r="923" ht="15.75" customHeight="1"/>
-    <row r="924" ht="15.75" customHeight="1"/>
-    <row r="925" ht="15.75" customHeight="1"/>
-    <row r="926" ht="15.75" customHeight="1"/>
-    <row r="927" ht="15.75" customHeight="1"/>
-    <row r="928" ht="15.75" customHeight="1"/>
-    <row r="929" ht="15.75" customHeight="1"/>
-    <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
-    <row r="935" ht="15.75" customHeight="1"/>
-    <row r="936" ht="15.75" customHeight="1"/>
-    <row r="937" ht="15.75" customHeight="1"/>
-    <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
-    <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
-    <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>

--- a/JsonConverter/ExcelFiles/Quest.xlsx
+++ b/JsonConverter/ExcelFiles/Quest.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{814894F0-75CF-4FB2-ABE9-4BC5EB1B4246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="255" yWindow="1515" windowWidth="28185" windowHeight="12795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_Quest" sheetId="1" r:id="rId1"/>

--- a/JsonConverter/ExcelFiles/Quest.xlsx
+++ b/JsonConverter/ExcelFiles/Quest.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SunnyHoGaming\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{814894F0-75CF-4FB2-ABE9-4BC5EB1B4246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBF50A10-2D6D-467B-90F1-50FA8049896C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="255" yWindow="1515" windowWidth="28185" windowHeight="12795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_Quest" sheetId="1" r:id="rId1"/>
@@ -168,10 +168,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>픽서 부르미 획득하기:Item:Item_Map_01|폭주한 픽서 진정시키기 (1):Task:FixerCalm_1|폭주한 픽서 진정시키기 (2):Task:FixerCalm_2|폭주한 픽서 진정시키기 (3):Task:FixerCalm_3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>픽서에게 식당에서 음식 픽업 업무 시키기:FoodSupply</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -193,6 +189,10 @@
   </si>
   <si>
     <t>픽서가 가지고온 위성전화로 지구와 통신하자!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>픽서 부르미 획득하기:Item:Item_Map_01|폭주한 픽서 볼트 진정시키기:Task:FixerCalm_1|폭주한 픽서 픽스 진정시키기:Task:FixerCalm_2|폭주한 픽서 암스트숏 진정시키기:Task:FixerCalm_3</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -655,7 +655,7 @@
         <v>30</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>36</v>
@@ -681,7 +681,7 @@
         <v>37</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15.75" customHeight="1">
@@ -701,10 +701,10 @@
         <v>34</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15.75" customHeight="1">
@@ -724,10 +724,10 @@
         <v>32</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15.75" customHeight="1">
@@ -747,7 +747,7 @@
         <v>33</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G8" s="10" t="s">
         <v>35</v>
